--- a/מערכות שעות - גורדון.xlsx
+++ b/מערכות שעות - גורדון.xlsx
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>מרים</t>
+          <t>אינס</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>אינס</t>
+          <t>מרים</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>ד אינס</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="E293" s="3" t="inlineStr">
